--- a/docs/q1-eu-validation/avanzosc-eu-validation-2026-04-30.xlsx
+++ b/docs/q1-eu-validation/avanzosc-eu-validation-2026-04-30.xlsx
@@ -530,303 +530,303 @@
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="19" customHeight="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Avanzosc · Q1 — Validación lingüística EU</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="19" customHeight="1">
       <c r="B2" s="2" t="inlineStr"/>
     </row>
-    <row r="3">
+    <row r="3" ht="19" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Generado: 2026-04-30 · Total strings pendientes: 201</t>
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="19" customHeight="1">
       <c r="B4" s="2" t="inlineStr"/>
     </row>
-    <row r="5">
+    <row r="5" ht="19" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t>1. ¿Qué es esto?</t>
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="49" customHeight="1">
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Las traducciones al euskera del nuevo sitio web de Avanzosc están actualmente en estado DRAFT (borrador automático generado por el dev). Necesitamos que el equipo de Avanzosc las revise y corrija lo que haga falta antes de publicar la web en producción.</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="19" customHeight="1">
       <c r="B7" s="2" t="inlineStr"/>
     </row>
-    <row r="8">
+    <row r="8" ht="19" customHeight="1">
       <c r="B8" s="3" t="inlineStr">
         <is>
           <t>2. ¿Qué tienes que hacer?</t>
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="19" customHeight="1">
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Por cada fila de las pestañas siguientes:</t>
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="19" customHeight="1">
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  · Lee la columna ES (source) — el texto original en castellano.</t>
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="19" customHeight="1">
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  · Lee la columna EU DRAFT (current) — la traducción actual generada.</t>
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="19" customHeight="1">
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  · Si la traducción está bien: dejar la columna EU FINAL VACÍA. (Vacío = aprobamos la draft.)</t>
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="19" customHeight="1">
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  · Si la traducción debe corregirse: escribir la versión correcta en la columna EU FINAL.</t>
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="19" customHeight="1">
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  · Si tienes dudas, variantes alternativas o quieres comentar algo: usar la columna Notas.</t>
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="19" customHeight="1">
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  · La columna Contexto te dice DÓNDE aparece la string (URL/snippet) — útil para desambiguar duplicados.</t>
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="19" customHeight="1">
       <c r="B16" s="2" t="inlineStr"/>
     </row>
-    <row r="17">
+    <row r="17" ht="19" customHeight="1">
       <c r="B17" s="3" t="inlineStr">
         <is>
           <t>3. Glosario (NO traducir, mantener literal en EU también)</t>
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="19" customHeight="1">
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  · Avanzosc · Odoo · OdooMRP · OCA · OpenERP · OpenUpgrade · TinyERP</t>
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="19" customHeight="1">
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  · Kit Consulting · Kit Digital (programas Red.es; nombres oficiales)</t>
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="19" customHeight="1">
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  · ERP · MRP · CRM · POS · EDI · ADR · AECOC · SILICIE · SAT (siglas técnicas)</t>
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="19" customHeight="1">
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  · CIF · S.L. (datos legales)</t>
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="19" customHeight="1">
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  · Direcciones de email, números de teléfono, URLs, IDs (todos literales)</t>
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="19" customHeight="1">
       <c r="B23" s="2" t="inlineStr"/>
     </row>
-    <row r="24">
+    <row r="24" ht="19" customHeight="1">
       <c r="B24" s="3" t="inlineStr">
         <is>
           <t>4. Tono y registro</t>
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="34" customHeight="1">
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>B2B profesional cercano. Tutear (zu) coherente con el ES original. Evitar palabras coloquiales pero también evitar registro excesivamente formal/burocrático. Imitar el tono de la columna ES.</t>
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="19" customHeight="1">
       <c r="B26" s="2" t="inlineStr"/>
     </row>
-    <row r="27">
+    <row r="27" ht="19" customHeight="1">
       <c r="B27" s="3" t="inlineStr">
         <is>
           <t>5. Bloque Legal — IMPORTANTE</t>
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="49" customHeight="1">
       <c r="B28" s="4" t="inlineStr">
         <is>
           <t>⚠ La pestaña «Legal (Q3 — ESPERAR asesoría)» NO se revisa todavía. Esos textos son las páginas legales (aviso, privacidad, cookies) y dependen de revisión por la asesoría legal de Avanzosc (gate Q3). Cuando la asesoría valide los textos ES base, ese bloque se reabrirá. Por ahora dejarlo COMO ESTÁ (no editar).</t>
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="19" customHeight="1">
       <c r="B29" s="2" t="inlineStr"/>
     </row>
-    <row r="30">
+    <row r="30" ht="19" customHeight="1">
       <c r="B30" s="3" t="inlineStr">
         <is>
           <t>6. Cómo devolver el archivo</t>
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="19" customHeight="1">
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  · Guardar el XLSX con los cambios (mismo formato XLSX, NO PDF, NO Word).</t>
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="34" customHeight="1">
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  · Devolverlo al desarrollador (Aner / equipo dev). El dev parsea la columna EU FINAL, mergea al fichero de traducciones del módulo (i18n/eu.po), levanta el flag DRAFT y verifica que la web sigue funcionando.</t>
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="19" customHeight="1">
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  · El dev puede preguntar dudas concretas si una entrada en Notas necesita aclaración.</t>
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="19" customHeight="1">
       <c r="B34" s="2" t="inlineStr"/>
     </row>
-    <row r="35">
+    <row r="35" ht="19" customHeight="1">
       <c r="B35" s="3" t="inlineStr">
         <is>
           <t>7. Atención a duplicados</t>
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="49" customHeight="1">
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Si una misma string ES aparece en varias filas (puede ocurrir si está en varios sitios de la web), los IDs Q1-XXXXXX serán DISTINTOS pero el ES idéntico. Decisión: traducir igual en ambas filas. Si la columna Contexto sugiere matices, traducir distinto y anotar el porqué en Notas.</t>
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="19" customHeight="1">
       <c r="B37" s="2" t="inlineStr"/>
     </row>
-    <row r="38">
+    <row r="38" ht="19" customHeight="1">
       <c r="B38" s="3" t="inlineStr">
         <is>
           <t>8. Resumen visual</t>
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="19" customHeight="1">
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  · Strings pendientes total: 201</t>
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="19" customHeight="1">
       <c r="B40" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  · Legal — ESPERAR Q3: 23 strings  ⚠ ESPERAR Q3</t>
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="19" customHeight="1">
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  · Contacto: 32 strings  </t>
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="19" customHeight="1">
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  · Conócenos / Equipo / Empleo: 47 strings  </t>
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="19" customHeight="1">
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  · Soluciones (4 sectoriales): 51 strings  </t>
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="19" customHeight="1">
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  · Transversales: 2 strings  </t>
         </is>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="19" customHeight="1">
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  · Hero &amp; Home: 34 strings  </t>
         </is>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="19" customHeight="1">
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  · Navegación &amp; Footer: 12 strings  </t>
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="19" customHeight="1">
       <c r="B47" s="2" t="inlineStr"/>
     </row>
-    <row r="48">
+    <row r="48" ht="19" customHeight="1">
       <c r="B48" s="3" t="inlineStr">
         <is>
           <t>9. Convención del color amarillo claro</t>
         </is>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="19" customHeight="1">
       <c r="B49" s="6" t="inlineStr">
         <is>
           <t>Las celdas con fondo amarillo claro son las que tú rellenas (EU FINAL y Notas).</t>
@@ -856,28 +856,28 @@
     <col width="45" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="19" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Legal — ESPERAR Q3</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="19" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Bloque LEGAL DRAFT. Esperar revisión Q3 por asesoría legal antes de tocar. Solo informativo.</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="19" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
           <t>⚠ ESPERAR Q3 ASESORÍA — bloque informativo, NO editar todavía</t>
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="19" customHeight="1">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>ID</t>
@@ -909,7 +909,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="19" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Q1-64640E</t>
@@ -933,7 +933,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="19" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Q1-A660D3</t>
@@ -957,7 +957,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="19" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Q1-E4301D</t>
@@ -981,7 +981,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="19" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Q1-69C173</t>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="19" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Q1-D3CF24</t>
@@ -1029,7 +1029,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="19" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Q1-2BB564</t>
@@ -1053,7 +1053,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="19" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Q1-23EB5E</t>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="19" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Q1-F9AD42</t>
@@ -1101,7 +1101,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="19" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Q1-7EE697</t>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="19" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Q1-5179FA</t>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="19" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Q1-5592FE</t>
@@ -1173,7 +1173,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="19" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Q1-1E4C11</t>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="19" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Q1-91CEFC</t>
@@ -1221,7 +1221,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="19" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Q1-A4F8D3</t>
@@ -1245,7 +1245,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="19" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Q1-07F10C</t>
@@ -1269,7 +1269,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="19" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Q1-53E564</t>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="19" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Q1-774A3E</t>
@@ -1317,7 +1317,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="139" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
           <t>Q1-4A0902</t>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="19" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Q1-6ADE47</t>
@@ -1369,7 +1369,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="34" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
           <t>Q1-1C11EC</t>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="34" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Q1-6C0661</t>
@@ -1417,7 +1417,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="79" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
           <t>Q1-008203</t>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="94" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Q1-EE4641</t>
@@ -1497,21 +1497,21 @@
     <col width="45" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="19" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Contacto</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="19" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Página /contacto + /contacto/gracias + CTA contacto transversal.</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="19" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
           <t>ID</t>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="19" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Q1-813486</t>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="19" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Q1-84ED7A</t>
@@ -1591,7 +1591,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="34" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Q1-2CD1C2</t>
@@ -1615,7 +1615,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="34" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Q1-25256E</t>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="34" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Q1-1A2F3C</t>
@@ -1663,7 +1663,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="34" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Q1-8ECE21</t>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="19" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Q1-2CA5A6</t>
@@ -1711,7 +1711,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="19" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Q1-04F478</t>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="19" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Q1-04F478</t>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="19" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Q1-84ADD5</t>
@@ -1783,7 +1783,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="19" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Q1-84ADD5</t>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="19" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Q1-6EB94B</t>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="34" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Q1-7B1BDC</t>
@@ -1855,7 +1855,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="19" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Q1-46344C</t>
@@ -1879,7 +1879,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="64" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Q1-49896C</t>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="49" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Q1-151342</t>
@@ -1929,7 +1929,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="34" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Q1-EF1AD3</t>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="19" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Q1-EBA5FF</t>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="19" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
           <t>Q1-2E7108</t>
@@ -2001,7 +2001,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="19" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Q1-EB9E23</t>
@@ -2025,7 +2025,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="34" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
           <t>Q1-ACA002</t>
@@ -2049,7 +2049,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="19" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Q1-E68491</t>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="19" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
           <t>Q1-99AF37</t>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="19" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Q1-99AF37</t>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="34" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
           <t>Q1-7B3261</t>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="19" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Q1-E7D934</t>
@@ -2169,7 +2169,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="19" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
           <t>Q1-D6E35C</t>
@@ -2193,7 +2193,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="19" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Q1-99D319</t>
@@ -2217,7 +2217,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="19" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
           <t>Q1-1AFB11</t>
@@ -2241,7 +2241,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="19" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
           <t>Q1-0A8001</t>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="34" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
           <t>Q1-255264</t>
@@ -2289,7 +2289,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="64" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
           <t>Q1-255264</t>
@@ -2342,21 +2342,21 @@
     <col width="45" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="19" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Conócenos / Equipo / Empleo</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="19" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Páginas Conócenos y Empleo + snippet equipo.</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="19" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
           <t>ID</t>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="34" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Q1-3D2065</t>
@@ -2412,7 +2412,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="34" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Q1-A4F3FB</t>
@@ -2436,7 +2436,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="64" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Q1-794909</t>
@@ -2460,7 +2460,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="19" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Q1-C61662</t>
@@ -2484,7 +2484,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="34" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Q1-B65C9F</t>
@@ -2508,7 +2508,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="34" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Q1-7275E7</t>
@@ -2532,7 +2532,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="19" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Q1-0AC175</t>
@@ -2556,7 +2556,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="34" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Q1-C62F12</t>
@@ -2580,7 +2580,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="19" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Q1-C1B655</t>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="19" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Q1-C718BD</t>
@@ -2628,7 +2628,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="19" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Q1-553D30</t>
@@ -2652,7 +2652,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="64" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Q1-9B5367</t>
@@ -2677,7 +2677,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="19" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Q1-4F5FDF</t>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="19" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Q1-CA3E55</t>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="19" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Q1-52868C</t>
@@ -2749,7 +2749,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="34" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Q1-F1A866</t>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="19" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Q1-F1A866</t>
@@ -2797,7 +2797,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="79" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Q1-0211CE</t>
@@ -2821,7 +2821,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="49" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
           <t>Q1-D6D96D</t>
@@ -2845,7 +2845,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="19" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Q1-CB0D8C</t>
@@ -2869,7 +2869,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="19" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
           <t>Q1-CC7951</t>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="34" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Q1-CD317A</t>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="19" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
           <t>Q1-778C1E</t>
@@ -2941,7 +2941,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="19" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Q1-3C4D94</t>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="64" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
           <t>Q1-5D5059</t>
@@ -2991,7 +2991,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="19" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Q1-CDB1C7</t>
@@ -3015,7 +3015,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="19" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
           <t>Q1-17D808</t>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="34" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Q1-6534B0</t>
@@ -3063,7 +3063,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="19" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
           <t>Q1-F9B067</t>
@@ -3087,7 +3087,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="34" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
           <t>Q1-8F8823</t>
@@ -3111,7 +3111,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="19" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
           <t>Q1-B20BE4</t>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="19" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
           <t>Q1-447B1A</t>
@@ -3159,7 +3159,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="34" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
           <t>Q1-4F8EC3</t>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="19" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
           <t>Q1-9C1AA8</t>
@@ -3207,7 +3207,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="19" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
         <is>
           <t>Q1-C20F02</t>
@@ -3231,7 +3231,7 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="79" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Q1-40C529</t>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="79" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
         <is>
           <t>Q1-A55ED6</t>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="19" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
           <t>Q1-4B0790</t>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="19" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
         <is>
           <t>Q1-493DF2</t>
@@ -3329,7 +3329,7 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="19" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
           <t>Q1-53D17C</t>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="19" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
         <is>
           <t>Q1-CBC02F</t>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="19" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
           <t>Q1-5117BA</t>
@@ -3401,7 +3401,7 @@
         </is>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="19" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
         <is>
           <t>Q1-7E51EB</t>
@@ -3425,7 +3425,7 @@
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="19" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
         <is>
           <t>Q1-543A13</t>
@@ -3449,7 +3449,7 @@
         </is>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="19" customHeight="1">
       <c r="A48" s="11" t="inlineStr">
         <is>
           <t>Q1-21EDFB</t>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="19" customHeight="1">
       <c r="A49" s="11" t="inlineStr">
         <is>
           <t>Q1-46F1C6</t>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="19" customHeight="1">
       <c r="A50" s="11" t="inlineStr">
         <is>
           <t>Q1-F47F6B</t>
@@ -3548,21 +3548,21 @@
     <col width="45" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="19" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Soluciones (4 sectoriales)</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="19" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>4 páginas sectoriales + snippet sector_specifics + caso éxito archetype 1.</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="19" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
           <t>ID</t>
@@ -3594,7 +3594,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="19" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Q1-BC719E</t>
@@ -3618,7 +3618,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="34" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Q1-3CDC0F</t>
@@ -3642,7 +3642,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="34" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Q1-84BE8B</t>
@@ -3666,7 +3666,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="34" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Q1-945485</t>
@@ -3690,7 +3690,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="199" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Q1-40E4D2</t>
@@ -3720,7 +3720,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="34" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Q1-49A8C0</t>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="34" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Q1-2860FF</t>
@@ -3768,7 +3768,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="34" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Q1-0A0C14</t>
@@ -3792,7 +3792,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="34" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Q1-774E95</t>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="34" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Q1-ABC25C</t>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="34" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Q1-338BAD</t>
@@ -3864,7 +3864,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="34" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Q1-9D0D86</t>
@@ -3888,7 +3888,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="34" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Q1-8412C2</t>
@@ -3912,7 +3912,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="34" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Q1-E60F1A</t>
@@ -3936,7 +3936,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="34" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Q1-2B7014</t>
@@ -3960,7 +3960,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="49" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Q1-769D6C</t>
@@ -3984,7 +3984,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="34" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Q1-2E43FE</t>
@@ -4008,7 +4008,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="34" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Q1-8B5E13</t>
@@ -4032,7 +4032,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="49" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
           <t>Q1-BB1886</t>
@@ -4056,7 +4056,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="79" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Q1-7DB3CF</t>
@@ -4081,7 +4081,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="34" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
           <t>Q1-4187AB</t>
@@ -4105,7 +4105,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="34" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Q1-059430</t>
@@ -4129,7 +4129,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="34" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
           <t>Q1-4D613D</t>
@@ -4153,7 +4153,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="34" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Q1-CC1490</t>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="34" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
           <t>Q1-253271</t>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="34" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Q1-74C9C1</t>
@@ -4225,7 +4225,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="34" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
           <t>Q1-D3ED14</t>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="19" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Q1-101C08</t>
@@ -4273,7 +4273,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="394" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
           <t>Q1-E5DFCE</t>
@@ -4309,7 +4309,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="34" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
           <t>Q1-553975</t>
@@ -4333,7 +4333,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="49" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
           <t>Q1-FDD7B8</t>
@@ -4357,7 +4357,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="34" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
           <t>Q1-30583C</t>
@@ -4381,7 +4381,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="34" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
           <t>Q1-0BE3A9</t>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="34" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
           <t>Q1-292642</t>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="34" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
         <is>
           <t>Q1-06ED8D</t>
@@ -4453,7 +4453,7 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="19" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Q1-2F48A9</t>
@@ -4477,7 +4477,7 @@
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="34" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
         <is>
           <t>Q1-7C6C82</t>
@@ -4501,7 +4501,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="34" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
           <t>Q1-4CCAC7</t>
@@ -4525,7 +4525,7 @@
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="34" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
         <is>
           <t>Q1-A91C61</t>
@@ -4549,7 +4549,7 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="34" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
           <t>Q1-3FD608</t>
@@ -4573,7 +4573,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="34" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
         <is>
           <t>Q1-AE4E3C</t>
@@ -4597,7 +4597,7 @@
         </is>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="34" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
           <t>Q1-3D4451</t>
@@ -4621,7 +4621,7 @@
         </is>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="19" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
         <is>
           <t>Q1-C5CA6E</t>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="34" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
         <is>
           <t>Q1-222DC2</t>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="34" customHeight="1">
       <c r="A48" s="11" t="inlineStr">
         <is>
           <t>Q1-04666C</t>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="34" customHeight="1">
       <c r="A49" s="11" t="inlineStr">
         <is>
           <t>Q1-FE191C</t>
@@ -4717,7 +4717,7 @@
         </is>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="34" customHeight="1">
       <c r="A50" s="11" t="inlineStr">
         <is>
           <t>Q1-F45767</t>
@@ -4741,7 +4741,7 @@
         </is>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="34" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
         <is>
           <t>Q1-F1D091</t>
@@ -4765,7 +4765,7 @@
         </is>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="34" customHeight="1">
       <c r="A52" s="11" t="inlineStr">
         <is>
           <t>Q1-6D71C5</t>
@@ -4789,7 +4789,7 @@
         </is>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="34" customHeight="1">
       <c r="A53" s="11" t="inlineStr">
         <is>
           <t>Q1-BF8196</t>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="49" customHeight="1">
       <c r="A54" s="11" t="inlineStr">
         <is>
           <t>Q1-79C841</t>
@@ -4864,21 +4864,21 @@
     <col width="45" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="19" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Transversales</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="19" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Snippets transversales (CTA Kit Consulting) que aparecen en múltiples páginas.</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="19" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
           <t>ID</t>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="34" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Q1-2AD7E4</t>
@@ -4934,7 +4934,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="94" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Q1-481C97</t>
@@ -4987,21 +4987,21 @@
     <col width="45" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="19" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Hero &amp; Home</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="19" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Snippets visibles en la home: hero principal, pilares, sectores grid, contador, timeline.</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="19" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
           <t>ID</t>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="34" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Q1-2A8C21</t>
@@ -5057,7 +5057,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="34" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Q1-F3C682</t>
@@ -5081,7 +5081,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="49" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Q1-DB5275</t>
@@ -5105,7 +5105,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="34" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Q1-43C225</t>
@@ -5129,7 +5129,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="34" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Q1-0FD7F8</t>
@@ -5153,7 +5153,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="34" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Q1-62C27A</t>
@@ -5177,7 +5177,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="34" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Q1-A7A423</t>
@@ -5201,7 +5201,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="19" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Q1-463178</t>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="49" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Q1-EA9128</t>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="34" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Q1-4BC042</t>
@@ -5273,7 +5273,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="34" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Q1-C310BF</t>
@@ -5297,7 +5297,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="64" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Q1-7068A2</t>
@@ -5322,7 +5322,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="34" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Q1-CD317A</t>
@@ -5346,7 +5346,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="34" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Q1-43CEBA</t>
@@ -5370,7 +5370,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="34" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Q1-565E98</t>
@@ -5394,7 +5394,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="34" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Q1-42EFAD</t>
@@ -5418,7 +5418,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="34" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Q1-B7BAB4</t>
@@ -5442,7 +5442,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="34" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Q1-3BC4F2</t>
@@ -5466,7 +5466,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="34" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
           <t>Q1-D4E8A8</t>
@@ -5490,7 +5490,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="34" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Q1-08F199</t>
@@ -5514,7 +5514,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="34" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
           <t>Q1-3070B4</t>
@@ -5538,7 +5538,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="49" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Q1-F90964</t>
@@ -5562,7 +5562,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="34" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
           <t>Q1-50B06E</t>
@@ -5586,7 +5586,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="34" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Q1-EAB055</t>
@@ -5610,7 +5610,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="34" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
           <t>Q1-1076CD</t>
@@ -5634,7 +5634,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="34" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Q1-BD90FE</t>
@@ -5658,7 +5658,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="34" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
           <t>Q1-19D7F9</t>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="34" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Q1-0D31A5</t>
@@ -5706,7 +5706,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="34" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
           <t>Q1-1EE964</t>
@@ -5730,7 +5730,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="19" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
           <t>Q1-35B4FD</t>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="49" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
           <t>Q1-51D3E4</t>
@@ -5778,7 +5778,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="34" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
           <t>Q1-F53D9E</t>
@@ -5802,7 +5802,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="19" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
           <t>Q1-44DB32</t>
@@ -5826,7 +5826,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="34" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
           <t>Q1-99D319</t>
@@ -5877,21 +5877,21 @@
     <col width="45" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="19" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Navegación &amp; Footer</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="19" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Menú principal (top-level + dropdown) + header buttons + footer columns.</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="19" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
           <t>ID</t>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="19" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Q1-4A0902</t>
@@ -5947,7 +5947,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="34" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Q1-D8A53E</t>
@@ -5971,7 +5971,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="34" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Q1-98CAFF</t>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="49" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Q1-E0E325</t>
@@ -6020,7 +6020,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="19" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Q1-6EB94B</t>
@@ -6044,7 +6044,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="19" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Q1-61D267</t>
@@ -6068,7 +6068,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="34" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Q1-4F70D8</t>
@@ -6092,7 +6092,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="19" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Q1-902C91</t>
@@ -6116,7 +6116,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="19" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Q1-008203</t>
@@ -6140,7 +6140,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="19" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Q1-EE4641</t>
@@ -6164,7 +6164,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="34" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Q1-C24C1A</t>
@@ -6188,7 +6188,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="19" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Q1-754711</t>

--- a/docs/q1-eu-validation/avanzosc-eu-validation-2026-04-30.xlsx
+++ b/docs/q1-eu-validation/avanzosc-eu-validation-2026-04-30.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legal — ESPERAR Q3" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contacto" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conócenos - Equipo - Empleo" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conócenos - Equipo" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Soluciones (4 sectoriales)" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transversales" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hero &amp; Home" sheetId="7" state="visible" r:id="rId7"/>
@@ -543,7 +543,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 2026-04-30 · Total strings pendientes: 201</t>
+          <t>Generado: 2026-04-30 · Total strings pendientes: 180</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="39" ht="19" customHeight="1">
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Strings pendientes total: 201</t>
+          <t xml:space="preserve">  · Strings pendientes total: 180</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
     <row r="42" ht="19" customHeight="1">
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Conócenos / Equipo / Empleo: 47 strings  </t>
+          <t xml:space="preserve">  · Conócenos / Equipo: 27 strings  </t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
     <row r="46" ht="19" customHeight="1">
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Navegación &amp; Footer: 12 strings  </t>
+          <t xml:space="preserve">  · Navegación &amp; Footer: 11 strings  </t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2345,14 +2345,14 @@
     <row r="1" ht="19" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Conócenos / Equipo / Empleo</t>
+          <t>Conócenos / Equipo</t>
         </is>
       </c>
     </row>
     <row r="2" ht="19" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Páginas Conócenos y Empleo + snippet equipo.</t>
+          <t>Página Conócenos + snippet equipo. La página /trabaja-con-nosotros se eliminó post-v1 (sesión 2026-04-30) y sus 21 strings dejaron de estar en el .po.</t>
         </is>
       </c>
     </row>
@@ -2412,1112 +2412,632 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="64" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>Q1-A4F3FB</t>
+          <t>Q1-794909</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Actualmente sin vacantes formales abiertas. Si tu perfil encaja con los anteriores, escríbenos a</t>
+          <t>Avanzosc nació en 2008 en Azkoitia (Gipuzkoa) cuando OpenERP era todavía una alternativa minoritaria. Hoy seguimos en el mismo sitio, con más experiencia y un equipo más grande, pero la misma forma de trabajar.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Une honetan lan-eskaintza formalik gabe. Zure profila aurrekoekin bat badator, idatzi gugana</t>
+          <t>Avanzosc 2008an jaio zen Azkoitian (Gipuzkoa), OpenERP oraindik aukera gutxietsia zenean. Gaur leku berean jarraitzen dugu, esperientzia gehiagorekin eta talde handiago batekin, baina lan egiteko modu berarekin.</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr"/>
       <c r="E5" s="12" t="inlineStr"/>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>/trabaja-con-nosotros — Trabaja párrafo vacantes (con placeholder email).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="64" customHeight="1">
+          <t>/conocenos — Conocenos historia párrafo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="19" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>Q1-794909</t>
+          <t>Q1-C61662</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Avanzosc nació en 2008 en Azkoitia (Gipuzkoa) cuando OpenERP era todavía una alternativa minoritaria. Hoy seguimos en el mismo sitio, con más experiencia y un equipo más grande, pero la misma forma de trabajar.</t>
+          <t>Azkoitia como base, OCA Days como punto de encuentro.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Avanzosc 2008an jaio zen Azkoitian (Gipuzkoa), OpenERP oraindik aukera gutxietsia zenean. Gaur leku berean jarraitzen dugu, esperientzia gehiagorekin eta talde handiago batekin, baina lan egiteko modu berarekin.</t>
+          <t>Azkoitia oinarri gisa, OCA Days topagune gisa.</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr"/>
       <c r="E6" s="12" t="inlineStr"/>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>/conocenos — Conocenos historia párrafo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="19" customHeight="1">
+          <t>/conocenos — Conocenos valor 4 texto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>Q1-C61662</t>
+          <t>Q1-B65C9F</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Azkoitia como base, OCA Days como punto de encuentro.</t>
+          <t>Azkoitia, Gipuzkoa</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Azkoitia oinarri gisa, OCA Days topagune gisa.</t>
+          <t>Azkoitia, Gipuzkoa</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr"/>
       <c r="E7" s="12" t="inlineStr"/>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>/conocenos — Conocenos valor 4 texto.</t>
+          <t>Snippet: Equipo (home) — Task 3.9 equipo stat value sede.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>Q1-B65C9F</t>
+          <t>Q1-7275E7</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Azkoitia, Gipuzkoa</t>
+          <t>Composición</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Azkoitia, Gipuzkoa</t>
+          <t>Konposizioa</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr"/>
       <c r="E8" s="12" t="inlineStr"/>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Snippet: Equipo (home) — Task 3.9 equipo stat value sede.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="34" customHeight="1">
+          <t>Snippet: Equipo (home) — Task 3.9 equipo stat label «Composición».</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="19" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>Q1-7275E7</t>
+          <t>Q1-0AC175</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Composición</t>
+          <t>Comunidad OCA</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Konposizioa</t>
+          <t>OCA komunitatea</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr"/>
       <c r="E9" s="12" t="inlineStr"/>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>Snippet: Equipo (home) — Task 3.9 equipo stat label «Composición».</t>
+          <t>/conocenos — Conocenos valor 2 título.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>Q1-0AC175</t>
+          <t>Q1-C1B655</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Comunidad OCA</t>
+          <t>Conoce al equipo →</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>OCA komunitatea</t>
+          <t>Ezagutu taldea →</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr"/>
       <c r="E10" s="12" t="inlineStr"/>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>/conocenos — Conocenos valor 2 título.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="34" customHeight="1">
+          <t>/conocenos — Conocenos link al snippet equipo en home.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="79" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>Q1-C62F12</t>
+          <t>Q1-9B5367</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>con tu CV y 3 líneas sobre por qué te interesa Avanzosc.</t>
+          <t>Contribuyentes activos</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>zure CVarekin eta zergatik Avanzosc interesatzen zaizun azaltzen duten 3 lerrorekin.</t>
+          <t>Ekarpen aktiboak</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr"/>
       <c r="E11" s="12" t="inlineStr"/>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>/trabaja-con-nosotros — Trabaja párrafo vacantes cierre.</t>
+          <t>Snippet: Equipo (home) — Task 3.9 equipo stat OCA value.
+Label «OCA» NO se traduce (acrónimo internacional Odoo Community
+Association).</t>
         </is>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>Q1-C1B655</t>
+          <t>Q1-CA3E55</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Conoce al equipo →</t>
+          <t>Devolvemos lo que aprendemos. 600+ módulos publicados.</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Ezagutu taldea →</t>
+          <t>Ikasten duguna itzultzen dugu. 600+ modulu argitaratuak.</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr"/>
       <c r="E12" s="12" t="inlineStr"/>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>/conocenos — Conocenos link al snippet equipo en home.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="19" customHeight="1">
+          <t>/conocenos — Conocenos valor 2 texto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>Q1-C718BD</t>
+          <t>Q1-F1A866</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Consultora/or funcional distribución</t>
+          <t>Equipo</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Banaketa-aholkulari funtzionala</t>
+          <t>Taldea</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr"/>
       <c r="E13" s="12" t="inlineStr"/>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>/trabaja-con-nosotros — Trabaja perfil 3 label.</t>
+          <t>Snippet: Equipo (home) — Task 3.9 equipo stat label «Equipo».</t>
         </is>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Q1-553D30</t>
+          <t>Q1-F1A866</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Consultora/or funcional industrial</t>
+          <t>Equipo</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Industria-aholkulari funtzionala</t>
+          <t>Taldea</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr"/>
       <c r="E14" s="12" t="inlineStr"/>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>/trabaja-con-nosotros — Trabaja perfil 2 label.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="64" customHeight="1">
+          <t>/conocenos — Conocenos heading «Equipo».</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="79" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>Q1-9B5367</t>
+          <t>Q1-0211CE</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Contribuyentes activos</t>
+          <t>Equipo STEM con base en Azkoitia, Gipuzkoa. Mayoría femenina en un sector dominado por hombres. Programadoras, consultoras funcionales y técnicas de soporte. Contribuimos a la OCA y formamos a la siguiente generación a través de las academias.</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Ekarpen aktiboak</t>
+          <t>STEM taldea Azkoitian, Gipuzkoan. Emakume gehiengoa gizonek menderatutako sektore batean. Programatzaileak, kontsultore funtzionalak eta laguntza teknikariak. OCAri ekarpenak egiten ditugu eta hurrengo belaunaldia akademien bidez prestatzen dugu.</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr"/>
       <c r="E15" s="12" t="inlineStr"/>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>Snippet: Equipo (home) — Task 3.9 equipo stat OCA value.
-Label «OCA» NO se traduce (acrónimo internacional Odoo Community Association).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="19" customHeight="1">
+          <t>Snippet: Equipo (home) — Task 3.9 equipo párrafo principal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="49" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>Q1-4F5FDF</t>
+          <t>Q1-D6D96D</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Desarrolladora/or Odoo Python</t>
+          <t>Equipo STEM con base en Azkoitia. Mayoría femenina. Ingenieras, consultoras y técnicas que han pasado por planta, almacén y aula.</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Odoo Python garatzailea</t>
+          <t>STEM taldea Azkoitian. Gehiengoa emakumezkoa. Lantegitik, biltegitik eta gelatik igaro diren ingeniari, aholkulari eta teknikariak.</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr"/>
       <c r="E16" s="12" t="inlineStr"/>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>/trabaja-con-nosotros — Trabaja perfil 1 label.</t>
+          <t>/conocenos — Conocenos párrafo equipo.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>Q1-CA3E55</t>
+          <t>Q1-CC7951</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Devolvemos lo que aprendemos. 600+ módulos publicados.</t>
+          <t>Equipo STEM mayoritariamente femenino</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Ikasten duguna itzultzen dugu. 600+ modulu argitaratuak.</t>
+          <t>STEM taldea, gehienbat emakumezkoa</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr"/>
       <c r="E17" s="12" t="inlineStr"/>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>/conocenos — Conocenos valor 2 texto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="19" customHeight="1">
+          <t>/conocenos — Conocenos valor 3 título.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="49" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>Q1-52868C</t>
+          <t>Q1-CD317A</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Enviar CV</t>
+          <t>Hablar con nosotros</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>CVa bidali</t>
+          <t>Gurekin hitz egin</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr"/>
       <c r="E18" s="12" t="inlineStr"/>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>/trabaja-con-nosotros — Trabaja CTA2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="34" customHeight="1">
+          <t>/conocenos — Conocenos CTA2 (compartido con varias páginas Phase
+6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="19" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Q1-F1A866</t>
+          <t>Q1-778C1E</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Equipo</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Taldea</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr"/>
       <c r="E19" s="12" t="inlineStr"/>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>Snippet: Equipo (home) — Task 3.9 equipo stat label «Equipo».</t>
+          <t>/conocenos — Conocenos heading «Historia».</t>
         </is>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>Q1-F1A866</t>
+          <t>Q1-3C4D94</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Equipo</t>
+          <t>Honestidad técnica</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Taldea</t>
+          <t>Zintzotasun teknikoa</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr"/>
       <c r="E20" s="12" t="inlineStr"/>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>/conocenos — Conocenos heading «Equipo».</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="79" customHeight="1">
+          <t>/conocenos — Conocenos valor 1 título.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="64" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Q1-0211CE</t>
+          <t>Q1-5D5059</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Equipo STEM con base en Azkoitia, Gipuzkoa. Mayoría femenina en un sector dominado por hombres. Programadoras, consultoras funcionales y técnicas de soporte. Contribuimos a la OCA y formamos a la siguiente generación a través de las academias.</t>
+          <t>Implantamos Odoo en empresas industriales y de servicios, desde 2008.</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>STEM taldea Azkoitian, Gipuzkoan. Emakume gehiengoa gizonek menderatutako sektore batean. Programatzaileak, kontsultore funtzionalak eta laguntza teknikariak. OCAri ekarpenak egiten ditugu eta hurrengo belaunaldia akademien bidez prestatzen dugu.</t>
+          <t>Odoo industria eta zerbitzu enpresetan inplementatzen dugu, 2008tik.</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr"/>
       <c r="E21" s="12" t="inlineStr"/>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>Snippet: Equipo (home) — Task 3.9 equipo párrafo principal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="49" customHeight="1">
+          <t>/conocenos — hero, valores (4), historia, equipo
+----------------------------------------------------------------------------
+DRAFT - REVIEW NEEDED — Conocenos hero claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="19" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Q1-D6D96D</t>
+          <t>Q1-CDB1C7</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Equipo STEM con base en Azkoitia. Mayoría femenina. Ingenieras, consultoras y técnicas que han pasado por planta, almacén y aula.</t>
+          <t>Ingenieras que programan, configuran y forman.</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>STEM taldea Azkoitian. Gehiengoa emakumezkoa. Lantegitik, biltegitik eta gelatik igaro diren ingeniari, aholkulari eta teknikariak.</t>
+          <t>Programatu, konfiguratu eta prestatzen duten ingeniariak.</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr"/>
       <c r="E22" s="12" t="inlineStr"/>
       <c r="F22" s="11" t="inlineStr">
         <is>
-          <t>/conocenos — Conocenos párrafo equipo.</t>
+          <t>/conocenos — Conocenos valor 3 texto.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Q1-CB0D8C</t>
+          <t>Q1-17D808</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Equipo STEM en Azkoitia. Odoo, OCA, planta y aula.</t>
+          <t>Local pero conectado</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>STEM taldea Azkoitian. Odoo, OCA, lantegia eta gela.</t>
+          <t>Tokikoa baina konektatua</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr"/>
       <c r="E23" s="12" t="inlineStr"/>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>/trabaja-con-nosotros — Trabaja hero subtítulo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="19" customHeight="1">
+          <t>/conocenos — Conocenos valor 4 título.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="34" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Q1-CC7951</t>
+          <t>Q1-6534B0</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Equipo STEM mayoritariamente femenino</t>
+          <t>Mayoría STEM femenina</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>STEM taldea, gehienbat emakumezkoa</t>
+          <t>STEM gehiengo emakumea</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr"/>
       <c r="E24" s="12" t="inlineStr"/>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>/conocenos — Conocenos valor 3 título.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="34" customHeight="1">
+          <t>Snippet: Equipo (home) — Task 3.9 equipo stat value composición.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Q1-CD317A</t>
+          <t>Q1-447B1A</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Hablar con nosotros</t>
+          <t>Quiénes lo construyen</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Gurekin hitz egin</t>
+          <t>Nork eraikitzen duten</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr"/>
       <c r="E25" s="12" t="inlineStr"/>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>/conocenos — Conocenos CTA2 (compartido con varias páginas Phase 6).</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="19" customHeight="1">
+          <t>Snippet: Equipo (home) — Task 3.9 equipo heading.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="34" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>Q1-778C1E</t>
+          <t>Q1-4F8EC3</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Sede</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Egoitza</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr"/>
       <c r="E26" s="12" t="inlineStr"/>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>/conocenos — Conocenos heading «Historia».</t>
+          <t>Snippet: Equipo (home) — Task 3.9 equipo stat label «Sede».</t>
         </is>
       </c>
     </row>
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>Q1-3C4D94</t>
+          <t>Q1-9C1AA8</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Honestidad técnica</t>
+          <t>Si Odoo no es la solución, lo decimos.</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Zintzotasun teknikoa</t>
+          <t>Odoo ez bada irtenbidea, esan egiten dugu.</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr"/>
       <c r="E27" s="12" t="inlineStr"/>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>/conocenos — Conocenos valor 1 título.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="64" customHeight="1">
+          <t>/conocenos — Conocenos valor 1 texto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="19" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>Q1-5D5059</t>
+          <t>Q1-C20F02</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Implantamos Odoo en empresas industriales y de servicios, desde 2008.</t>
+          <t>Sin teatros. Con resultados medibles.</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Odoo industria eta zerbitzu enpresetan inplementatzen dugu, 2008tik.</t>
+          <t>Antzerkirik gabe. Emaitza neurgarriekin.</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr"/>
       <c r="E28" s="12" t="inlineStr"/>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>/conocenos — hero, valores (4), historia, equipo
-----------------------------------------------------------------------------
-DRAFT - REVIEW NEEDED — Conocenos hero claim.</t>
+          <t>/conocenos — Conocenos hero subtítulo.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="19" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>Q1-CDB1C7</t>
+          <t>Q1-53D17C</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Ingenieras que programan, configuran y forman.</t>
+          <t>Valores</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Programatu, konfiguratu eta prestatzen duten ingeniariak.</t>
+          <t>Balioak</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr"/>
       <c r="E29" s="12" t="inlineStr"/>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>/conocenos — Conocenos valor 3 texto.</t>
+          <t>/conocenos — Conocenos heading «Valores».</t>
         </is>
       </c>
     </row>
     <row r="30" ht="19" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>Q1-17D808</t>
+          <t>Q1-5117BA</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>Local pero conectado</t>
+          <t>Ver valores</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Tokikoa baina konektatua</t>
+          <t>Balioak ikusi</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr"/>
       <c r="E30" s="12" t="inlineStr"/>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>/conocenos — Conocenos valor 4 título.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="34" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>Q1-6534B0</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>Mayoría STEM femenina</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>STEM gehiengo emakumea</t>
-        </is>
-      </c>
-      <c r="D31" s="12" t="inlineStr"/>
-      <c r="E31" s="12" t="inlineStr"/>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>Snippet: Equipo (home) — Task 3.9 equipo stat value composición.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="19" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>Q1-F9B067</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>Perfiles que buscamos siempre</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>Beti bilatzen ditugun profilak</t>
-        </is>
-      </c>
-      <c r="D32" s="12" t="inlineStr"/>
-      <c r="E32" s="12" t="inlineStr"/>
-      <c r="F32" s="11" t="inlineStr">
-        <is>
-          <t>/trabaja-con-nosotros — Trabaja heading «Perfiles».</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="34" customHeight="1">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>Q1-8F8823</t>
-        </is>
-      </c>
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t>Por qué Avanzosc</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
-          <t>Zergatik Avanzosc</t>
-        </is>
-      </c>
-      <c r="D33" s="12" t="inlineStr"/>
-      <c r="E33" s="12" t="inlineStr"/>
-      <c r="F33" s="11" t="inlineStr">
-        <is>
-          <t>/trabaja-con-nosotros — Trabaja heading «Por qué Avanzosc».</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="19" customHeight="1">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t>Q1-B20BE4</t>
-        </is>
-      </c>
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>Practicantes (ingenierías STEM)</t>
-        </is>
-      </c>
-      <c r="C34" s="11" t="inlineStr">
-        <is>
-          <t>Praktiketako ikasleak (STEM ingeniaritzak)</t>
-        </is>
-      </c>
-      <c r="D34" s="12" t="inlineStr"/>
-      <c r="E34" s="12" t="inlineStr"/>
-      <c r="F34" s="11" t="inlineStr">
-        <is>
-          <t>/trabaja-con-nosotros — Trabaja perfil 5 label.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="19" customHeight="1">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>Q1-447B1A</t>
-        </is>
-      </c>
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t>Quiénes lo construyen</t>
-        </is>
-      </c>
-      <c r="C35" s="11" t="inlineStr">
-        <is>
-          <t>Nork eraikitzen duten</t>
-        </is>
-      </c>
-      <c r="D35" s="12" t="inlineStr"/>
-      <c r="E35" s="12" t="inlineStr"/>
-      <c r="F35" s="11" t="inlineStr">
-        <is>
-          <t>Snippet: Equipo (home) — Task 3.9 equipo heading.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="34" customHeight="1">
-      <c r="A36" s="11" t="inlineStr">
-        <is>
-          <t>Q1-4F8EC3</t>
-        </is>
-      </c>
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t>Sede</t>
-        </is>
-      </c>
-      <c r="C36" s="11" t="inlineStr">
-        <is>
-          <t>Egoitza</t>
-        </is>
-      </c>
-      <c r="D36" s="12" t="inlineStr"/>
-      <c r="E36" s="12" t="inlineStr"/>
-      <c r="F36" s="11" t="inlineStr">
-        <is>
-          <t>Snippet: Equipo (home) — Task 3.9 equipo stat label «Sede».</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="19" customHeight="1">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>Q1-9C1AA8</t>
-        </is>
-      </c>
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>Si Odoo no es la solución, lo decimos.</t>
-        </is>
-      </c>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
-          <t>Odoo ez bada irtenbidea, esan egiten dugu.</t>
-        </is>
-      </c>
-      <c r="D37" s="12" t="inlineStr"/>
-      <c r="E37" s="12" t="inlineStr"/>
-      <c r="F37" s="11" t="inlineStr">
-        <is>
-          <t>/conocenos — Conocenos valor 1 texto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="19" customHeight="1">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>Q1-C20F02</t>
-        </is>
-      </c>
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>Sin teatros. Con resultados medibles.</t>
-        </is>
-      </c>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>Antzerkirik gabe. Emaitza neurgarriekin.</t>
-        </is>
-      </c>
-      <c r="D38" s="12" t="inlineStr"/>
-      <c r="E38" s="12" t="inlineStr"/>
-      <c r="F38" s="11" t="inlineStr">
-        <is>
-          <t>/conocenos — Conocenos hero subtítulo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="79" customHeight="1">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>Q1-40C529</t>
-        </is>
-      </c>
-      <c r="B39" s="11" t="inlineStr">
-        <is>
-          <t>Trabaja con nosotros</t>
-        </is>
-      </c>
-      <c r="C39" s="11" t="inlineStr">
-        <is>
-          <t>Lan egin gurekin</t>
-        </is>
-      </c>
-      <c r="D39" s="12" t="inlineStr"/>
-      <c r="E39" s="12" t="inlineStr"/>
-      <c r="F39" s="11" t="inlineStr">
-        <is>
-          <t>/trabaja-con-nosotros — hero, por qué, perfiles, vacantes
-----------------------------------------------------------------------------
-DRAFT - REVIEW NEEDED — Trabaja hero claim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="79" customHeight="1">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t>Q1-A55ED6</t>
-        </is>
-      </c>
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t>Trabajamos con Odoo desde 2008. Cliente real, problemas reales, soluciones técnicas. Equipo mayoritariamente femenino en sector dominado por hombres. Contribución activa a OCA y formación interna continua. Sede en Azkoitia, presencial preferente con flexibilidad.</t>
-        </is>
-      </c>
-      <c r="C40" s="11" t="inlineStr">
-        <is>
-          <t>Odoo-rekin lan egiten dugu 2008tik. Bezero erreala, arazo errealak, irtenbide teknikoak. Gizonek nagusi diren sektorean, gure taldea gehienbat emakumezkoa da. OCAn ekarpen aktiboa eta etengabeko barneko prestakuntza. Egoitza Azkoitian, aurrez aurreko lana hobetsia, malgutasunarekin.</t>
-        </is>
-      </c>
-      <c r="D40" s="12" t="inlineStr"/>
-      <c r="E40" s="12" t="inlineStr"/>
-      <c r="F40" s="11" t="inlineStr">
-        <is>
-          <t>/trabaja-con-nosotros — Trabaja párrafo «Por qué».</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="19" customHeight="1">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>Q1-4B0790</t>
-        </is>
-      </c>
-      <c r="B41" s="11" t="inlineStr">
-        <is>
-          <t>Técnica/o de soporte L2</t>
-        </is>
-      </c>
-      <c r="C41" s="11" t="inlineStr">
-        <is>
-          <t>L2 laguntza-teknikaria</t>
-        </is>
-      </c>
-      <c r="D41" s="12" t="inlineStr"/>
-      <c r="E41" s="12" t="inlineStr"/>
-      <c r="F41" s="11" t="inlineStr">
-        <is>
-          <t>/trabaja-con-nosotros — Trabaja perfil 4 label.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="19" customHeight="1">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t>Q1-493DF2</t>
-        </is>
-      </c>
-      <c r="B42" s="11" t="inlineStr">
-        <is>
-          <t>Vacantes activas</t>
-        </is>
-      </c>
-      <c r="C42" s="11" t="inlineStr">
-        <is>
-          <t>Lan-eskaintza irekiak</t>
-        </is>
-      </c>
-      <c r="D42" s="12" t="inlineStr"/>
-      <c r="E42" s="12" t="inlineStr"/>
-      <c r="F42" s="11" t="inlineStr">
-        <is>
-          <t>/trabaja-con-nosotros — Trabaja heading «Vacantes».</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="19" customHeight="1">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>Q1-53D17C</t>
-        </is>
-      </c>
-      <c r="B43" s="11" t="inlineStr">
-        <is>
-          <t>Valores</t>
-        </is>
-      </c>
-      <c r="C43" s="11" t="inlineStr">
-        <is>
-          <t>Balioak</t>
-        </is>
-      </c>
-      <c r="D43" s="12" t="inlineStr"/>
-      <c r="E43" s="12" t="inlineStr"/>
-      <c r="F43" s="11" t="inlineStr">
-        <is>
-          <t>/conocenos — Conocenos heading «Valores».</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="19" customHeight="1">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>Q1-CBC02F</t>
-        </is>
-      </c>
-      <c r="B44" s="11" t="inlineStr">
-        <is>
-          <t>Ver perfiles</t>
-        </is>
-      </c>
-      <c r="C44" s="11" t="inlineStr">
-        <is>
-          <t>Profilak ikusi</t>
-        </is>
-      </c>
-      <c r="D44" s="12" t="inlineStr"/>
-      <c r="E44" s="12" t="inlineStr"/>
-      <c r="F44" s="11" t="inlineStr">
-        <is>
-          <t>/trabaja-con-nosotros — Trabaja CTA1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="19" customHeight="1">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t>Q1-5117BA</t>
-        </is>
-      </c>
-      <c r="B45" s="11" t="inlineStr">
-        <is>
-          <t>Ver valores</t>
-        </is>
-      </c>
-      <c r="C45" s="11" t="inlineStr">
-        <is>
-          <t>Balioak ikusi</t>
-        </is>
-      </c>
-      <c r="D45" s="12" t="inlineStr"/>
-      <c r="E45" s="12" t="inlineStr"/>
-      <c r="F45" s="11" t="inlineStr">
-        <is>
           <t>/conocenos — Conocenos CTA1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="19" customHeight="1">
-      <c r="A46" s="11" t="inlineStr">
-        <is>
-          <t>Q1-7E51EB</t>
-        </is>
-      </c>
-      <c r="B46" s="11" t="inlineStr">
-        <is>
-          <t>— backend, módulos custom, contribuciones OCA.</t>
-        </is>
-      </c>
-      <c r="C46" s="11" t="inlineStr">
-        <is>
-          <t>— backend, moduluak custom, OCAri ekarpenak.</t>
-        </is>
-      </c>
-      <c r="D46" s="12" t="inlineStr"/>
-      <c r="E46" s="12" t="inlineStr"/>
-      <c r="F46" s="11" t="inlineStr">
-        <is>
-          <t>/trabaja-con-nosotros — Trabaja perfil 1 texto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="19" customHeight="1">
-      <c r="A47" s="11" t="inlineStr">
-        <is>
-          <t>Q1-543A13</t>
-        </is>
-      </c>
-      <c r="B47" s="11" t="inlineStr">
-        <is>
-          <t>— bootcamp interno + proyectos reales.</t>
-        </is>
-      </c>
-      <c r="C47" s="11" t="inlineStr">
-        <is>
-          <t>— barneko bootcamp + benetako proiektuak.</t>
-        </is>
-      </c>
-      <c r="D47" s="12" t="inlineStr"/>
-      <c r="E47" s="12" t="inlineStr"/>
-      <c r="F47" s="11" t="inlineStr">
-        <is>
-          <t>/trabaja-con-nosotros — Trabaja perfil 5 texto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="19" customHeight="1">
-      <c r="A48" s="11" t="inlineStr">
-        <is>
-          <t>Q1-21EDFB</t>
-        </is>
-      </c>
-      <c r="B48" s="11" t="inlineStr">
-        <is>
-          <t>— debugging, comunicación cliente, formación.</t>
-        </is>
-      </c>
-      <c r="C48" s="11" t="inlineStr">
-        <is>
-          <t>— debugging, bezeroarekin komunikazioa, prestakuntza.</t>
-        </is>
-      </c>
-      <c r="D48" s="12" t="inlineStr"/>
-      <c r="E48" s="12" t="inlineStr"/>
-      <c r="F48" s="11" t="inlineStr">
-        <is>
-          <t>/trabaja-con-nosotros — Trabaja perfil 4 texto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="19" customHeight="1">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t>Q1-46F1C6</t>
-        </is>
-      </c>
-      <c r="B49" s="11" t="inlineStr">
-        <is>
-          <t>— MES, MRP, trazabilidad, integración planta.</t>
-        </is>
-      </c>
-      <c r="C49" s="11" t="inlineStr">
-        <is>
-          <t>— MES, MRP, trazabilitatea, lantegiarekin integrazioa.</t>
-        </is>
-      </c>
-      <c r="D49" s="12" t="inlineStr"/>
-      <c r="E49" s="12" t="inlineStr"/>
-      <c r="F49" s="11" t="inlineStr">
-        <is>
-          <t>/trabaja-con-nosotros — Trabaja perfil 2 texto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="19" customHeight="1">
-      <c r="A50" s="11" t="inlineStr">
-        <is>
-          <t>Q1-F47F6B</t>
-        </is>
-      </c>
-      <c r="B50" s="11" t="inlineStr">
-        <is>
-          <t>— WMS, picking, multi-canal.</t>
-        </is>
-      </c>
-      <c r="C50" s="11" t="inlineStr">
-        <is>
-          <t>— WMS, picking, kanal anitzekoa.</t>
-        </is>
-      </c>
-      <c r="D50" s="12" t="inlineStr"/>
-      <c r="E50" s="12" t="inlineStr"/>
-      <c r="F50" s="11" t="inlineStr">
-        <is>
-          <t>/trabaja-con-nosotros — Trabaja perfil 3 texto.</t>
         </is>
       </c>
     </row>
@@ -5418,7 +4938,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="34" customHeight="1">
+    <row r="20" ht="49" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Q1-B7BAB4</t>
@@ -5438,7 +4958,8 @@
       <c r="E20" s="12" t="inlineStr"/>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>Snippet: Pilares (home) — Task 3.1 pilar 3 (equipo STEM mayoritariamente femenino).</t>
+          <t>Snippet: Pilares (home) — Task 3.1 pilar 3 (equipo STEM mayoritariamente
+femenino).</t>
         </is>
       </c>
     </row>
@@ -5866,7 +5387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5995,141 +5516,140 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="49" customHeight="1">
+    <row r="7" ht="19" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>Q1-E0E325</t>
+          <t>Q1-6EB94B</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Empleo</t>
+          <t>Empresa</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lana</t>
+          <t>Enpresa</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr"/>
       <c r="E7" s="12" t="inlineStr"/>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>menu_trabaja · Footer (todas las páginas) — link footer columna Empresa + menú top-level
-(per pre-decisión Task 1.3)</t>
+          <t>Footer (todas las páginas) — heading columna 3</t>
         </is>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>Q1-6EB94B</t>
+          <t>Q1-61D267</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Empresa</t>
+          <t>Formación</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Enpresa</t>
+          <t>Formakuntza</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr"/>
       <c r="E8" s="12" t="inlineStr"/>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Footer (todas las páginas) — heading columna 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="19" customHeight="1">
+          <t>Menú: Formación — Task 2.2: menu top-level</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>Q1-61D267</t>
+          <t>Q1-4F70D8</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Formación</t>
+          <t>Inicio</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Formakuntza</t>
+          <t>Hasiera</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr"/>
       <c r="E9" s="12" t="inlineStr"/>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>Menú: Formación — Task 2.2: menu top-level</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1">
+          <t>Menú: Inicio — Task 2.2: menu top-level (data/menu.xml + paginas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="19" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>Q1-4F70D8</t>
+          <t>Q1-902C91</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Inicio</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Hasiera</t>
+          <t>Legala</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr"/>
       <c r="E10" s="12" t="inlineStr"/>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>Menú: Inicio — Task 2.2: menu top-level (data/menu.xml + paginas)</t>
+          <t>Footer (todas las páginas) — heading columna 4</t>
         </is>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>Q1-902C91</t>
+          <t>Q1-008203</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Política de Cookies</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Legala</t>
+          <t>Cookieen Politika</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr"/>
       <c r="E11" s="12" t="inlineStr"/>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>Footer (todas las páginas) — heading columna 4</t>
+          <t>Footer (todas las páginas) — link columna Legal</t>
         </is>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>Q1-008203</t>
+          <t>Q1-EE4641</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Política de Cookies</t>
+          <t>Política de Privacidad</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Cookieen Politika</t>
+          <t>Pribatutasun Politika</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr"/>
@@ -6140,73 +5660,49 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="19" customHeight="1">
+    <row r="13" ht="34" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>Q1-EE4641</t>
+          <t>Q1-C24C1A</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Política de Privacidad</t>
+          <t>Soluciones</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Pribatutasun Politika</t>
+          <t>Konponbideak</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr"/>
       <c r="E13" s="12" t="inlineStr"/>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>Footer (todas las páginas) — link columna Legal</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="34" customHeight="1">
+          <t>Menú: Soluciones (dropdown) · Footer (todas las páginas) — heading columna 2 footer + menú top-level</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="19" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Q1-C24C1A</t>
+          <t>Q1-754711</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Soluciones</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Konponbideak</t>
+          <t>Denda</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr"/>
       <c r="E14" s="12" t="inlineStr"/>
       <c r="F14" s="11" t="inlineStr">
-        <is>
-          <t>Menú: Soluciones (dropdown) · Footer (todas las páginas) — heading columna 2 footer + menú top-level</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>Q1-754711</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>Tienda</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Denda</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr"/>
-      <c r="E15" s="12" t="inlineStr"/>
-      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Menú: Tienda — Task 2.2: menu top-level</t>
         </is>
